--- a/results/classifica_run.xlsx
+++ b/results/classifica_run.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Per grandezza'!$A$1:$K$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Per Flesch-Kincaid'!$A$1:$K$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Per grandezza'!$A$1:$K$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Per Flesch-Kincaid'!$A$1:$K$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -902,12 +902,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>meta' + 2 bm25</t>
+          <t>due meta'</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>PlantUML</t>
+          <t>JSON compatto</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -919,22 +919,22 @@
         <v>54</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5475</v>
+        <v>0.551</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.4912</v>
+        <v>0.4904</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.6038</v>
+        <v>0.6115</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1126</v>
+        <v>0.1211</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -943,7 +943,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>parziale 50 %</t>
+          <t>meta' + 2 bm25</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -960,22 +960,22 @@
         <v>54</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5167</v>
+        <v>0.5475</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.4451</v>
+        <v>0.4912</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.5883</v>
+        <v>0.6038</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1433</v>
+        <v>0.1126</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -984,12 +984,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>parziale 25 %</t>
+          <t>parziale 75 %</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>PlantUML</t>
+          <t>JSON compatto</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1001,186 +1001,186 @@
         <v>54</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.462</v>
+        <v>0.545</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.3993</v>
+        <v>0.4699</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.6201</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.1254</v>
+        <v>0.1502</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="K12" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>parziale 50 %</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>PlantUML</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.5167</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.5883</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>3b random k3</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>meta' + 2 bm25</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.5809</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>parziale 50 %</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.4859</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.5445</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.1173</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>parziale 25 %</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>PlantUML</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>3b</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0.4495</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>0.3697</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>0.5292</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>0.1596</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>3b hybrid k3</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>PlantUML</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>3b</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>0.4351</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>0.3397</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>0.5306</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>0.1909</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>3b bm25 k3</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>PlantUML</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>3b</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>0.4331</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>0.3447</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>0.5216</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>0.1769</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.5247000000000001</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.1254</v>
+      </c>
+      <c r="J16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>3b static k2</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>PlantUML</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>3b</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>0.4259</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>0.3438</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>0.1612</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>16</v>
+      <c r="K16" s="2" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>3b bm25 k2</t>
+          <t>3b random k3</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1206,63 +1206,63 @@
         <v>54</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>0.425</v>
+        <v>0.4495</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.3505</v>
+        <v>0.3697</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.4994</v>
+        <v>0.5292</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.1489</v>
+        <v>0.1596</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K17" s="7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>parziale 25 %</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.5134</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.1415</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K18" s="2" t="n">
         <v>19</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>3b zero_shot</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>PlantUML</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>3b</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0.4244</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>0.3406</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>0.5082</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>0.1676</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>3b bm25 k3</t>
+          <t>3b hybrid k3</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>JSON compatto</t>
+          <t>PlantUML</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1288,63 +1288,63 @@
         <v>54</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.417</v>
+        <v>0.4351</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>0.3341</v>
+        <v>0.3397</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>0.5</v>
+        <v>0.5306</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>0.1659</v>
+        <v>0.1909</v>
       </c>
       <c r="J19" s="7" t="n">
         <v>23</v>
       </c>
       <c r="K19" s="7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>3b bm25 k3</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>PlantUML</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>0.5216</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="K20" s="7" t="n">
         <v>18</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>bm25 k3 senza attributi</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>PlantUML</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>controllo</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0.4143</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>0.3265</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>0.1755</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>JSON compatto</t>
+          <t>PlantUML</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1370,22 +1370,22 @@
         <v>53</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>0.4096</v>
+        <v>0.4259</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.3352</v>
+        <v>0.3438</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>0.4813</v>
+        <v>0.505</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>0.1461</v>
+        <v>0.1612</v>
       </c>
       <c r="J21" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K21" s="7" t="n">
         <v>21</v>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>3b random k3</t>
+          <t>3b bm25 k2</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>JSON compatto</t>
+          <t>PlantUML</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1411,22 +1411,22 @@
         <v>54</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.4087</v>
+        <v>0.425</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.3381</v>
+        <v>0.3505</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>0.4793</v>
+        <v>0.4994</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.1411</v>
+        <v>0.1489</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>3b hybrid k3</t>
+          <t>3b zero_shot</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>JSON compatto</t>
+          <t>PlantUML</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1452,22 +1452,22 @@
         <v>54</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0.4082</v>
+        <v>0.4244</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.3358</v>
+        <v>0.3406</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>0.4807</v>
+        <v>0.5082</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>0.1449</v>
+        <v>0.1676</v>
       </c>
       <c r="J23" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="K23" s="7" t="n">
         <v>20</v>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>3b bm25 k2</t>
+          <t>3b bm25 k3</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -1493,108 +1493,313 @@
         <v>54</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.4058</v>
+        <v>0.417</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.3434</v>
+        <v>0.3341</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>0.4683</v>
+        <v>0.5</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.1248</v>
+        <v>0.1659</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K24" s="7" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>bm25 k3 senza attributi</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>PlantUML</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.4143</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>3b static k2</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>0.4813</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>0.1461</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>3b random k3</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>0.4793</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>3b hybrid k3</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>3b bm25 k2</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>3b zero_shot</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>JSON compatto</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="E25" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F25" s="9" t="n">
+      <c r="E30" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>0.3716</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G30" s="10" t="n">
         <v>0.3348</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="H30" s="10" t="n">
         <v>0.4083</v>
       </c>
-      <c r="I25" s="11" t="n">
+      <c r="I30" s="11" t="n">
         <v>0.0735</v>
       </c>
-      <c r="J25" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="J30" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>bm25 k3 senza attributi</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>JSON compatto</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>controllo</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="F26" s="4" t="n">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F31" s="4" t="n">
         <v>0.3433</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G31" s="5" t="n">
         <v>0.2865</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H31" s="5" t="n">
         <v>0.4001</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I31" s="6" t="n">
         <v>0.1136</v>
       </c>
-      <c r="J26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>25</v>
+      <c r="J31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K26"/>
+  <autoFilter ref="A1:K31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1605,7 +1810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2003,7 +2208,7 @@
         <v>8</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2012,12 +2217,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>meta' + 2 bm25</t>
+          <t>due meta'</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>PlantUML</t>
+          <t>JSON compatto</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -2029,22 +2234,22 @@
         <v>54</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5475</v>
+        <v>0.551</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.5447</v>
+        <v>0.5728</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.5503</v>
+        <v>0.5291</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0056</v>
+        <v>-0.0438</v>
       </c>
       <c r="J10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2053,7 +2258,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>parziale 50 %</t>
+          <t>meta' + 2 bm25</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2070,22 +2275,22 @@
         <v>54</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5167</v>
+        <v>0.5475</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.5218</v>
+        <v>0.5447</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.5503</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-0.0102</v>
+        <v>0.0056</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -2094,203 +2299,203 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>parziale 75 %</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.5108</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>-0.06850000000000001</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>parziale 50 %</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>PlantUML</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.5167</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.5218</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.5116000000000001</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>meta' + 2 bm25</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.5289</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.0471</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>parziale 50 %</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.4859</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.5036</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.4681</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-0.0354</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>parziale 25 %</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>PlantUML</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>controllo</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="F12" s="4" t="n">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F16" s="4" t="n">
         <v>0.462</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>0.4632</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>0.4607</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I16" s="6" t="n">
         <v>-0.0025</v>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>3b random k3</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>PlantUML</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>3b</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0.4495</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>0.4489</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>-0.0012</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>3b hybrid k3</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>PlantUML</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>3b</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>0.4351</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>0.4418</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>0.4285</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>-0.0133</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" s="7" t="n">
+      <c r="J16" s="2" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>3b bm25 k3</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>PlantUML</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>3b</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>0.4331</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>0.4274</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>0.4388</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="K16" s="2" t="n">
         <v>15</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>3b static k2</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>PlantUML</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>3b</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>0.4259</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>0.4227</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>0.4293</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>0.0066</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -2299,7 +2504,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>3b bm25 k2</t>
+          <t>3b random k3</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -2316,63 +2521,63 @@
         <v>54</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>0.425</v>
+        <v>0.4495</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.4229</v>
+        <v>0.45</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.4271</v>
+        <v>0.4489</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0042</v>
+        <v>-0.0012</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>3b zero_shot</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>PlantUML</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>3b</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0.4244</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>0.4238</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>-0.0012</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>17</v>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>parziale 25 %</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>-0.0247</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -2381,80 +2586,80 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
+          <t>3b hybrid k3</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>PlantUML</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>0.4351</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>0.4418</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
           <t>3b bm25 k3</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>JSON compatto</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>PlantUML</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>0.4145</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>0.4196</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="E20" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="J20" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>bm25 k3 senza attributi</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>PlantUML</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>controllo</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0.4143</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>0.4164</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>0.4122</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>-0.0042</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>20</v>
+      <c r="K20" s="7" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -2468,7 +2673,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>JSON compatto</t>
+          <t>PlantUML</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2480,22 +2685,22 @@
         <v>53</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>0.4096</v>
+        <v>0.4259</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.4114</v>
+        <v>0.4227</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>0.4077</v>
+        <v>0.4293</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>-0.0037</v>
+        <v>0.0066</v>
       </c>
       <c r="J21" s="7" t="n">
         <v>22</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -2504,12 +2709,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>3b random k3</t>
+          <t>3b bm25 k2</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>JSON compatto</t>
+          <t>PlantUML</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -2521,22 +2726,22 @@
         <v>54</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.4087</v>
+        <v>0.425</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.4139</v>
+        <v>0.4229</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>0.4035</v>
+        <v>0.4271</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>-0.0104</v>
+        <v>0.0042</v>
       </c>
       <c r="J22" s="7" t="n">
         <v>21</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -2545,12 +2750,12 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>3b hybrid k3</t>
+          <t>3b zero_shot</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>JSON compatto</t>
+          <t>PlantUML</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2562,22 +2767,22 @@
         <v>54</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>0.4082</v>
+        <v>0.4244</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.4034</v>
+        <v>0.425</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>0.413</v>
+        <v>0.4238</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>0.0095</v>
+        <v>-0.0012</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -2586,7 +2791,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>3b bm25 k2</t>
+          <t>3b bm25 k3</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -2603,108 +2808,313 @@
         <v>54</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.4058</v>
+        <v>0.417</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.417</v>
+        <v>0.4145</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>0.3947</v>
+        <v>0.4196</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>-0.0224</v>
+        <v>0.0051</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K24" s="7" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>bm25 k3 senza attributi</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>PlantUML</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.4143</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>3b static k2</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>3b random k3</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>3b hybrid k3</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>3b bm25 k2</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>JSON compatto</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>-0.0224</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>3b zero_shot</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>JSON compatto</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="E25" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="F25" s="9" t="n">
+      <c r="E30" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>0.3716</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G30" s="10" t="n">
         <v>0.3681</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="H30" s="10" t="n">
         <v>0.375</v>
       </c>
-      <c r="I25" s="11" t="n">
+      <c r="I30" s="11" t="n">
         <v>0.0068</v>
       </c>
-      <c r="J25" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="J30" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>bm25 k3 senza attributi</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>JSON compatto</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>controllo</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="F26" s="4" t="n">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F31" s="4" t="n">
         <v>0.3433</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G31" s="5" t="n">
         <v>0.3417</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H31" s="5" t="n">
         <v>0.3448</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I31" s="6" t="n">
         <v>0.0031</v>
       </c>
-      <c r="J26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>25</v>
+      <c r="J31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K26"/>
+  <autoFilter ref="A1:K31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2759,7 +3169,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  static k2 ha 53 esercizi: AirTravel è uno dei due esempi fissi, quindi non ha questa condizione. Parziale e misti esistono solo in PlantUML.</t>
+          <t xml:space="preserve">  static k2 ha 53 esercizi: AirTravel è uno dei due esempi fissi, quindi non ha questa condizione. Parziale e misti: PlantUML (voci 163-165) e compatto (voce 170).</t>
         </is>
       </c>
     </row>

--- a/results/classifica_run.xlsx
+++ b/results/classifica_run.xlsx
@@ -3125,7 +3125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -3134,61 +3134,68 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Graduatoria di tutte le run sui 54 esercizi di validazione (Gemma 4 26B A4B QAT): i 6 prompt del passo 3b e i controlli oracle (solo analisi, voci 162-169).</t>
+          <t>Graduatoria di tutte le run sui 54 esercizi di validazione (Gemma 4 26B A4B QAT): i 6 prompt del passo 3b e i controlli oracle (solo analisi, voci 162-171).</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ordine: F1 sui 54 esercizi, decrescente. 'Posizione tra i difficili / facili' = posizione della run se la graduatoria si facesse solo su quella metà.</t>
+          <t xml:space="preserve">  Graduatoria DESCRITTIVA. L'analisi statistica riguarda solo le righe del 3b (azzurre, voce 172); le righe dei controlli oracle (verdi) sono escluse e vanno negli sviluppi futuri.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  F1 = media degli F1 di classi, attributi, relazioni e generalizzazioni (evaluation/element_metrics.py, abbinamento rilassato), prima sulle ripetizioni valide di ogni esercizio (3 nel 3b, 1 nei controlli), poi sugli esercizi: ogni esercizio pesa uguale. Metrica NOSTRA: lo strumento dei relatori ha valutato solo il 3b.</t>
+          <t xml:space="preserve">  Ordine: F1 sui 54 esercizi, decrescente. 'Posizione tra i difficili / facili' = posizione della run se la graduatoria si facesse solo su quella metà.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Metà più difficile / più facile: i 54 esercizi ordinati per difficoltà decrescente e divisi a metà (27 + 27). Flesch-Kincaid: metà difficile da 8.50 in su, metà facile fino a 8.30. Grandezza (classi + relazioni del GT): metà difficile da 18 elementi in su, metà facile fino a 18. A parità di valore decide l'altra difficoltà, poi il nome dell'esercizio. Primo foglio: la grandezza, difficoltà dominante.</t>
+          <t xml:space="preserve">  F1 = media degli F1 di classi, attributi, relazioni e generalizzazioni (evaluation/element_metrics.py, abbinamento rilassato), prima sulle ripetizioni valide di ogni esercizio (3 nel 3b, 1 nei controlli), poi sugli esercizi: ogni esercizio pesa uguale. Metrica NOSTRA: lo strumento dei relatori ha valutato solo il 3b.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Colore: azzurro = prompt del 3b (configurazioni reali); verde = controlli oracle, in cui l'esempio contiene la soluzione dell'esercizio, intera o in parte (non utilizzabili in un sistema reale: misurano un tetto).</t>
+          <t xml:space="preserve">  Metà più difficile / più facile: i 54 esercizi ordinati per difficoltà decrescente e divisi a metà (27 + 27). Flesch-Kincaid: metà difficile da 8.50 in su, metà facile fino a 8.30. Grandezza (classi + relazioni del GT): metà difficile da 18 elementi in su, metà facile fino a 18. A parità di valore decide l'altra difficoltà, poi il nome dell'esercizio. Primo foglio: la grandezza, difficoltà dominante.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  static k2 ha 53 esercizi: AirTravel è uno dei due esempi fissi, quindi non ha questa condizione. Parziale e misti: PlantUML (voci 163-165) e compatto (voce 170).</t>
+          <t xml:space="preserve">  Colore: azzurro = prompt del 3b (configurazioni reali); verde = controlli oracle, in cui l'esempio contiene la soluzione dell'esercizio, intera o in parte (non utilizzabili in un sistema reale: misurano un tetto).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Risposte non valide escluse: PlantUML / 3b zero_shot: 1; JSON compatto / 3b zero_shot: 2; JSON compatto / 3b random k3: 1; JSON compatto / 3b bm25 k2: 1; JSON compatto / 3b bm25 k3: 1.</t>
+          <t xml:space="preserve">  static k2 ha 53 esercizi: AirTravel è uno dei due esempi fissi, quindi non ha questa condizione. Parziale e misti: PlantUML (voci 163-165) e compatto (voce 170).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tutte le run presenti.</t>
+          <t xml:space="preserve">  Risposte non valide escluse: PlantUML / 3b zero_shot: 1; JSON compatto / 3b zero_shot: 2; JSON compatto / 3b random k3: 1; JSON compatto / 3b bm25 k2: 1; JSON compatto / 3b bm25 k3: 1.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tutte le run presenti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  Generato da experiments/build_results.py.</t>
         </is>
